--- a/data/stats/supp_tables/fallcover-soilcover-cctill-pairs.xlsx
+++ b/data/stats/supp_tables/fallcover-soilcover-cctill-pairs.xlsx
@@ -11,6 +11,62 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="17">
+  <si>
+    <t>contrast</t>
+  </si>
+  <si>
+    <t>cctrt_id</t>
+  </si>
+  <si>
+    <t>odds.ratio</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>z.ratio</t>
+  </si>
+  <si>
+    <t>p.value</t>
+  </si>
+  <si>
+    <t>inversion / notill</t>
+  </si>
+  <si>
+    <t>mix_E</t>
+  </si>
+  <si>
+    <t>Inf</t>
+  </si>
+  <si>
+    <t>inversion / surface</t>
+  </si>
+  <si>
+    <t>notill / surface</t>
+  </si>
+  <si>
+    <t>mix_M</t>
+  </si>
+  <si>
+    <t>nocc</t>
+  </si>
+  <si>
+    <t>rad_L</t>
+  </si>
+  <si>
+    <t>rad_M</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,526 +410,420 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>contrast</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cctrt_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds.ratio</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>z.ratio</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>inversion / notill</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>1.516090285245578</v>
+        <v>1.516084599620692</v>
       </c>
       <c r="D2">
-        <v>0.1803518297508889</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1803513331851133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3.498151306203524</v>
+        <v>3.498116293772504</v>
       </c>
       <c r="H2">
-        <v>0.001360803963655788</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>inversion / surface</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
+        <v>0.00136098048091049</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>1.640938767784557</v>
+        <v>1.640932862719048</v>
       </c>
       <c r="D3">
-        <v>0.1942985414752995</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.194298008244638</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4.182765715857165</v>
+        <v>4.182731751181277</v>
       </c>
       <c r="H3">
-        <v>8.539453711842171E-05</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>notill / surface</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
+        <v>8.540724648875564E-05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>1.082348976016791</v>
+        <v>1.082349140100488</v>
       </c>
       <c r="D4">
-        <v>0.1209883908052317</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1209886245982933</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0.7079210835766223</v>
+        <v>0.7079211791328285</v>
       </c>
       <c r="H4">
-        <v>0.758806166397747</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>inversion / notill</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
+        <v>0.7588061099166554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>0.86995541010283</v>
+        <v>0.869961515749351</v>
       </c>
       <c r="D5">
-        <v>0.0928515662318108</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.09285236902576249</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>-1.305270148602413</v>
+        <v>-1.30520226737227</v>
       </c>
       <c r="H5">
-        <v>0.3921911572046244</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inversion / surface</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
+        <v>0.3922292077871175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>1.066018001636587</v>
+        <v>1.066022448726439</v>
       </c>
       <c r="D6">
-        <v>0.1123647988923362</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1123654882247938</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.6065134120969735</v>
+        <v>0.6065517985554369</v>
       </c>
       <c r="H6">
-        <v>0.8165606541632984</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>notill / surface</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
+        <v>0.8165397234199927</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>1.225370851490633</v>
+        <v>1.225367363300213</v>
       </c>
       <c r="D7">
-        <v>0.1303164449296127</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1303162578911086</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1.911107247937667</v>
+        <v>1.911077783563653</v>
       </c>
       <c r="H7">
-        <v>0.1354958057196167</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inversion / notill</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
+        <v>0.1355040981032944</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>0.8219285693169557</v>
+        <v>0.8219289567611026</v>
       </c>
       <c r="D8">
-        <v>0.08769660932045731</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.08769679593145524</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>-1.837946323562494</v>
+        <v>-1.837938860955228</v>
       </c>
       <c r="H8">
-        <v>0.1572860721277639</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inversion / surface</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
+        <v>0.1572884191556503</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>0.9960655282915155</v>
+        <v>0.9960622100344051</v>
       </c>
       <c r="D9">
-        <v>0.1050335278401664</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1050333894850012</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>-0.03738541001545286</v>
+        <v>-0.03741692706659563</v>
       </c>
       <c r="H9">
-        <v>0.9992297238502468</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>notill / surface</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
+        <v>0.999228425075031</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>1.211863859555669</v>
+        <v>1.211859251144397</v>
       </c>
       <c r="D10">
-        <v>0.1293335571185433</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1293332737742115</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>1.800547547275295</v>
+        <v>1.800509012892927</v>
       </c>
       <c r="H10">
-        <v>0.1693733449019755</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>inversion / notill</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
+        <v>0.1693861367348479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>0.6650183790192303</v>
+        <v>0.665019102087703</v>
       </c>
       <c r="D11">
-        <v>0.07011593983959581</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.07011612482741589</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>-3.869134434915896</v>
+        <v>-3.869118121369963</v>
       </c>
       <c r="H11">
-        <v>0.000321532757985743</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>inversion / surface</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
+        <v>0.0003215541213783535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>0.9126948740393238</v>
+        <v>0.9126954417490013</v>
       </c>
       <c r="D12">
-        <v>0.09431504573091537</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.09431526248335527</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>-0.8840372463181814</v>
+        <v>-0.8840297452551397</v>
       </c>
       <c r="H12">
-        <v>0.650397955379742</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>notill / surface</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
+        <v>0.6504026955850895</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>1.372435563939401</v>
+        <v>1.372434925378481</v>
       </c>
       <c r="D13">
-        <v>0.1450714848513064</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1450716293585828</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>2.99504194999215</v>
+        <v>2.995033171389587</v>
       </c>
       <c r="H13">
-        <v>0.007729781434557714</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>inversion / notill</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
+        <v>0.007729998516349923</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>0.6396071085793811</v>
+        <v>0.639606692391809</v>
       </c>
       <c r="D14">
-        <v>0.06773408243214341</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.06773414486566563</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>-4.220049402663848</v>
+        <v>-4.220048911333656</v>
       </c>
       <c r="H14">
-        <v>7.247459465198336E-05</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>inversion / surface</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
+        <v>7.247475198146613E-05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>0.8921976132275939</v>
+        <v>0.8921971712735979</v>
       </c>
       <c r="D15">
-        <v>0.09250223924911134</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.09250233987257994</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>-1.100198971920891</v>
+        <v>-1.100202007902519</v>
       </c>
       <c r="H15">
-        <v>0.5139300926755109</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>notill / surface</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
+        <v>0.5139282092944064</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>1.39491509906642</v>
+        <v>1.394915315750101</v>
       </c>
       <c r="D16">
-        <v>0.1482987517443051</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1482990079136915</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>3.13067063915815</v>
+        <v>3.130667178725829</v>
       </c>
       <c r="H16">
-        <v>0.004962390282731599</v>
+        <v>0.004962447572254503</v>
       </c>
     </row>
   </sheetData>
